--- a/class_diagram/service/成績管理sys_クラス図_service.xlsx
+++ b/class_diagram/service/成績管理sys_クラス図_service.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29622"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri_sys\seiseki_manage_sys\class_diagram\service\manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{CB110E73-D601-408B-AFCE-4F5FC9A78A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23B1F349-8EDE-4F5D-8063-95CE8787C2A4}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{CB110E73-D601-408B-AFCE-4F5FC9A78A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1FF6E7F-7CB8-4096-BF73-C76FE02BC05C}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -524,6 +524,191 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>repository : ManagersRepository</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0BD1F3A-DFE9-4727-BB8F-7DD6D256CEED}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{DB7C34A3-F3F4-47F2-9EE9-2D01DFCAD0AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5181600" y="2990850"/>
+          <a:ext cx="3733800" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getManagerById(  id :  Integer )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r Manager</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>

--- a/class_diagram/service/成績管理sys_クラス図_service.xlsx
+++ b/class_diagram/service/成績管理sys_クラス図_service.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri_sys\seiseki_manage_sys\class_diagram\service\manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{CB110E73-D601-408B-AFCE-4F5FC9A78A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1FF6E7F-7CB8-4096-BF73-C76FE02BC05C}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="13_ncr:1_{CB110E73-D601-408B-AFCE-4F5FC9A78A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5521DC1A-8307-4B1A-B927-48BAA1B21AF6}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ManagerService" sheetId="3" r:id="rId1"/>
     <sheet name="SubjectService" sheetId="4" r:id="rId2"/>
     <sheet name="MajorService" sheetId="2" r:id="rId3"/>
     <sheet name="ClassService" sheetId="5" r:id="rId4"/>
+    <sheet name="ClassSubjectService" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -6570,6 +6571,1509 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>-r List&lt;ClassEntity&gt;</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BCF98DC-9060-4EEB-B61F-796BA8EB92A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="733425"/>
+          <a:ext cx="18468975" cy="7105650"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassSubjectService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B696830-3139-45DC-BADC-47F4106C8002}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{0BCF98DC-9060-4EEB-B61F-796BA8EB92A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="942975" y="2590800"/>
+          <a:ext cx="3267075" cy="723900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getClassSubjectById( id  : Integer)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r ClassSubject</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="四角形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1704BA60-912D-4DCC-A2A2-E639FD752059}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{413E8CE2-57A8-4012-981E-D7715A22D04C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7334250" y="1352550"/>
+          <a:ext cx="5695950" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>subjectService : SubjectService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="四角形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFFC09FA-61C5-474C-BF2E-A53104B3933C}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{1704BA60-912D-4DCC-A2A2-E639FD752059}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7343775" y="857250"/>
+          <a:ext cx="5695950" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>classService : ClassService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="四角形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E828ABEE-157C-4D3A-B180-DC59B788B122}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{7734DB75-0FE1-4335-A24B-9E94A8A4BF33}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7334250" y="1847850"/>
+          <a:ext cx="5695950" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>managerService : ManagerService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="四角形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A32CA029-0A3E-459D-A6B1-2617468722D3}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E828ABEE-157C-4D3A-B180-DC59B788B122}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13163550" y="1847850"/>
+          <a:ext cx="5695950" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>repository : ClassSubjectsRepository</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="四角形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B80E457-C91D-4B4A-BE72-C46B9842D5FA}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A32CA029-0A3E-459D-A6B1-2617468722D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4295775" y="2590800"/>
+          <a:ext cx="3267075" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getClassSubjectsByClassId( classId  : Integer)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r List&lt;ClassSubject&gt;</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="四角形 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E772DA36-61ED-4CCB-92F8-E0E019C2543D}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{8B80E457-C91D-4B4A-BE72-C46B9842D5FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4286250" y="3714750"/>
+          <a:ext cx="3267075" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>registerClassSubject( form  : ClassSubjectAddForm)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r ClassSubject</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="四角形 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F478E807-B403-4A32-9CFA-AD817A1A8555}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E772DA36-61ED-4CCB-92F8-E0E019C2543D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="923925" y="3714750"/>
+          <a:ext cx="3267075" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>deleteClassSubjectById(  id : Integer )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r </a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -6937,4 +8441,15 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB8FE1E5-4210-437E-9C2D-106306B92B23}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>